--- a/Dataset/1_label/UP_UP_V1_5 divisions_per_second.xlsx
+++ b/Dataset/1_label/UP_UP_V1_5 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D321"/>
+  <dimension ref="A1:D324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6210,6 +6210,60 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>UP_UP_V1_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>66000</v>
+      </c>
+      <c r="C322" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>UP_UP_V1_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>66200</v>
+      </c>
+      <c r="C323" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>UP_UP_V1_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>66400</v>
+      </c>
+      <c r="C324" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
